--- a/InputData/bldgs/SoBRCBbG/Shr of Blgd Rtrft Cost Borne by Govt.xlsx
+++ b/InputData/bldgs/SoBRCBbG/Shr of Blgd Rtrft Cost Borne by Govt.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\bldgs\SoBRCBbG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\bldgs\SoBRCBbG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{107AC2A6-81B2-4E9B-8126-021B7368DEC8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD9BBFC-3794-49CA-A6B7-E4003BB4BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="75" windowWidth="24090" windowHeight="14700" xr2:uid="{B7370FBA-4486-4F99-AF7A-4FA274821588}"/>
+    <workbookView xWindow="15420" yWindow="885" windowWidth="21420" windowHeight="19980" activeTab="1" xr2:uid="{B7370FBA-4486-4F99-AF7A-4FA274821588}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SoBRCBbG" sheetId="2" r:id="rId2"/>
+    <sheet name="Green Remodeling" sheetId="3" r:id="rId2"/>
+    <sheet name="SoBRCBbG" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,62 +36,181 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>This variable specifies the share of the cost for retrofitting existing buildings</t>
+  </si>
+  <si>
+    <t>under the EPS's accelerated building retrofitting policy that will be borne</t>
+  </si>
+  <si>
+    <t>government already pays 100% of the retrofit cost.</t>
+  </si>
+  <si>
+    <t>by the government.  It does not apply to government-owned buildings, where</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (share of cost)</t>
+  </si>
+  <si>
+    <t>urban residential</t>
+  </si>
+  <si>
+    <t>rural residential</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
+    <t>Government Cost Share</t>
+  </si>
   <si>
     <t>SoBRCBbG Share of Building Retrofit Costs Borne by Government</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>U.S. Department of Energy</t>
-  </si>
-  <si>
-    <t>https://www.energystar.gov/about/federal_tax_credits/non_business_energy_property_tax_credits</t>
-  </si>
-  <si>
-    <t>Equipment Tax Credits for Primary Residences</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>This variable specifies the share of the cost for retrofitting existing buildings</t>
-  </si>
-  <si>
-    <t>under the EPS's accelerated building retrofitting policy that will be borne</t>
-  </si>
-  <si>
-    <t>government already pays 100% of the retrofit cost.</t>
-  </si>
-  <si>
-    <t>by the government.  It does not apply to government-owned buildings, where</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (share of cost)</t>
-  </si>
-  <si>
-    <t>urban residential</t>
-  </si>
-  <si>
-    <t>rural residential</t>
-  </si>
-  <si>
-    <t>commercial</t>
-  </si>
-  <si>
-    <t>Government Cost Share</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>LH</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>공동 avg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>단독 avg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>residential average :</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> * 그린리모델링 사업의 상환 방식은 원금균등 상환임</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green remodelling projects</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Private buildings</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>South Korea has a building retrofit cost support mechanism called "Green Remodelling Projects".</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Since the real support costs can vary by the loan period, we used the averaged value. </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loan month (month)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commercial</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Residential</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>House</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Complex</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loan support (%)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Share of govt. support of the total repayment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenremodeling.or.kr/support/sup1000.asp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This project </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">4% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">of loan interest. </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> ** 100만원 대출 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% 이자 지원금 비율로 계산함 (네이버 이자 계산기의 대출이자계산 기능을 이용함)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -98,7 +218,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -106,7 +226,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -114,17 +234,86 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -140,18 +329,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -167,9 +386,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -207,7 +426,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -313,7 +532,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -455,7 +674,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -463,65 +682,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01810828-2E37-43FF-9A71-F4460C03E7FB}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{E1B5812F-3104-4D2A-8EFF-45948AF0F1E7}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{FECF6A79-F6E8-4C4F-9D97-D6F32B4171C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -529,49 +764,445 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17301020-6E33-4FBF-8306-93C4662876BD}">
+  <dimension ref="A2:S22"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="17" max="17" width="12.625" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:19" ht="66" x14ac:dyDescent="0.3">
+      <c r="D2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="4">
+        <v>120</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11">
+        <f>206000/1206000</f>
+        <v>0.17081260364842454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4">
+        <v>60</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3</v>
+      </c>
+      <c r="G4" s="18">
+        <f>103000/1103000</f>
+        <v>9.3381686310063466E-2</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="16">
+        <f>AVERAGE(G4:G7)</f>
+        <v>5.2706973639581739E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="4">
+        <v>36</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3</v>
+      </c>
+      <c r="G5" s="18">
+        <f>61000/1061000</f>
+        <v>5.7492931196983975E-2</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="4">
+        <v>24</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3</v>
+      </c>
+      <c r="G6" s="18">
+        <f>41000/1041000</f>
+        <v>3.9385206532180597E-2</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="4">
+        <v>12</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3</v>
+      </c>
+      <c r="G7" s="18">
+        <f>21000/1021000</f>
+        <v>2.0568070519098921E-2</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4">
+        <v>60</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3</v>
+      </c>
+      <c r="G8" s="18">
+        <f>103000/1103000</f>
+        <v>9.3381686310063466E-2</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="16">
+        <f>AVERAGE(G8:G9)</f>
+        <v>7.5437308753523724E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="4">
+        <v>36</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3</v>
+      </c>
+      <c r="G9" s="18">
+        <f>61000/1061000</f>
+        <v>5.7492931196983975E-2</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="G10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12">
+        <f>AVERAGE(I4:I9)</f>
+        <v>6.4072141196552732E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="H8:H9"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF72B00-B157-41C5-B107-14ECB7FAB6F3}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="1" max="1" width="39.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <f>'Green Remodeling'!I10</f>
+        <v>6.4072141196552732E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <f>'Green Remodeling'!I10</f>
+        <v>6.4072141196552732E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>0.1</v>
+        <f>'Green Remodeling'!G3</f>
+        <v>0.17081260364842454</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{417BFE65-820B-4C98-9667-FA243900F7C2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A05AFF5A-BBFD-4312-A568-94CFD67DE638}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB76387C-A69D-421D-9648-FC3042475D2B}"/>
 </file>